--- a/export-service/templates/DRP_template.xlsx
+++ b/export-service/templates/DRP_template.xlsx
@@ -1,15 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10426"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pranvil/01_coding/defect-forecast-review/export-service/templates/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA437008-2A9B-D54B-BC7D-6A4DDCFAA13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView xWindow="5920" yWindow="10380" windowWidth="51200" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRP Plan" sheetId="1" r:id="rId1"/>
   </sheets>
   <externalReferences>
+    <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
@@ -25,9 +32,9 @@
     <externalReference r:id="rId15"/>
     <externalReference r:id="rId16"/>
     <externalReference r:id="rId17"/>
-    <externalReference r:id="rId18"/>
   </externalReferences>
   <definedNames>
+    <definedName name="_1">#REF!</definedName>
     <definedName name="_Toc">#REF!</definedName>
     <definedName name="_Toc182012204_2">#REF!</definedName>
     <definedName name="_Toc182012204_2_4">#REF!</definedName>
@@ -82,7 +89,6 @@
     <definedName name="xx">'[15]Risk Codes'!$C$7:$F$7</definedName>
     <definedName name="模块名">[16]Component一览!$B$2:$B$113</definedName>
     <definedName name="優先順位の定義">#REF!</definedName>
-    <definedName name="_1">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
@@ -107,18 +113,19 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Ronggao, YANG(R&amp;D SPC SPMD-SZ-TCT)</author>
   </authors>
   <commentList>
-    <comment ref="A2" authorId="0">
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Ronggao, YANG(R&amp;D SPC SPMD-SZ-TCT):</t>
@@ -127,6 +134,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -139,13 +147,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="61">
   <si>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>项目名</t>
@@ -166,6 +175,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>部门</t>
@@ -264,6 +274,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>系统质量二部</t>
@@ -273,7 +284,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>-</t>
     </r>
@@ -282,6 +293,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>运营商系统测试组</t>
@@ -293,6 +305,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>系统质量二部</t>
@@ -302,7 +315,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>-</t>
     </r>
@@ -311,6 +324,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>北美需求交付组</t>
@@ -325,6 +339,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>专项与协议测试部</t>
@@ -334,7 +349,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>-</t>
     </r>
@@ -343,6 +358,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>运营商专项测试二组</t>
@@ -354,6 +370,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>专项与协议测试部</t>
@@ -363,7 +380,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>-</t>
     </r>
@@ -372,6 +389,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>运营商协议测试一组</t>
@@ -383,6 +401,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>流水线</t>
@@ -400,6 +419,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>累计创建</t>
@@ -414,6 +434,7 @@
         <sz val="8"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>协议技术部</t>
@@ -425,6 +446,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>底软技术部</t>
@@ -436,6 +458,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>系统技术部</t>
@@ -447,6 +470,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>运营商应用开发部</t>
@@ -458,6 +482,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>基础应用开发部</t>
@@ -469,6 +494,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>独立应用开发部</t>
@@ -480,6 +506,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>工程效能部</t>
@@ -491,6 +518,7 @@
         <sz val="8"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>终端</t>
@@ -500,7 +528,7 @@
         <sz val="8"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>OS</t>
     </r>
@@ -509,6 +537,7 @@
         <sz val="8"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>部</t>
@@ -526,6 +555,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>累计解决</t>
@@ -537,6 +567,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>遗留</t>
@@ -546,98 +577,26 @@
     <t>Backlog</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">MV </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>版本</t>
-    </r>
-  </si>
-  <si>
-    <t>FC checklist</t>
-  </si>
-  <si>
-    <t>M1-1</t>
-  </si>
-  <si>
-    <t>M1-2</t>
-  </si>
-  <si>
-    <t>M1-3</t>
-  </si>
-  <si>
-    <t>M1-4</t>
-  </si>
-  <si>
-    <t>M1-5</t>
-  </si>
-  <si>
-    <t>M2</t>
-  </si>
-  <si>
-    <t>M3</t>
-  </si>
-  <si>
-    <t>M4</t>
-  </si>
-  <si>
-    <t>M5-1</t>
-  </si>
-  <si>
-    <t>M5-L</t>
-  </si>
-  <si>
-    <t>V1</t>
-  </si>
-  <si>
-    <t>V2</t>
-  </si>
-  <si>
-    <t>V3</t>
-  </si>
-  <si>
-    <t>V4</t>
-  </si>
-  <si>
-    <t>4/16 SR4A</t>
-  </si>
-  <si>
-    <t>6/8 SR5</t>
+    <t>MV 版本</t>
   </si>
   <si>
     <t>问题提交率</t>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>问题解决率</t>
-  </si>
-  <si>
-    <t>DSI&lt;544</t>
-  </si>
-  <si>
-    <t>DSI&lt;136</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试完成率</t>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="11">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="7">
     <numFmt numFmtId="176" formatCode="[$-409]d\-mmm;@"/>
     <numFmt numFmtId="177" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
     <numFmt numFmtId="178" formatCode="[$-409]mmm/yy;@"/>
@@ -646,7 +605,7 @@
     <numFmt numFmtId="181" formatCode="yyyy/m"/>
     <numFmt numFmtId="182" formatCode="0.0_);[Red]\(0.0\)"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -658,30 +617,31 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -689,195 +649,77 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -892,19 +734,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.0999786370433668"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -916,19 +758,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.599993896298105"/>
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCE3C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.349986266670736"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -946,174 +782,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFD2ECFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFDECEF2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1226,272 +912,91 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="53">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyBorder="0"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyBorder="0"/>
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="27" fillId="0" borderId="0" applyBorder="0"/>
-    <xf numFmtId="177" fontId="27" fillId="0" borderId="0" applyBorder="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="178" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="179" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="6" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1538,193 +1043,50 @@
     <xf numFmtId="180" fontId="2" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="6" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="53">
+  <cellStyles count="5">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
-    <cellStyle name="常规 2 2" xfId="50"/>
-    <cellStyle name="常规 3" xfId="51"/>
-    <cellStyle name="常规 4" xfId="52"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="常规 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="常规 4" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="00DDDDDD"/>
-      <color rgb="00777777"/>
-      <color rgb="00E5F6FF"/>
-      <color rgb="00000000"/>
+      <color rgb="FFDECEF2"/>
+      <color rgb="FFD2ECFF"/>
+      <color rgb="FFCF9CF4"/>
+      <color rgb="FFDDDDDD"/>
+      <color rgb="FF777777"/>
+      <color rgb="FFE5F6FF"/>
+      <color rgb="FF000000"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="BOM评审"/>
     </sheetNames>
@@ -1736,8 +1098,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Historical"/>
       <sheetName val="Yippee 3G 2nd source matrix"/>
@@ -1753,8 +1118,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Contents"/>
       <sheetName val="Changes and New"/>
@@ -1844,8 +1212,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Criteria"/>
       <sheetName val="Table"/>
@@ -1973,8 +1344,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
     </sheetNames>
@@ -1986,8 +1360,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
     </sheetNames>
@@ -1999,8 +1376,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="EP Top Risks"/>
       <sheetName val="Master Risk Matrix"/>
@@ -2042,8 +1422,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Unicom"/>
       <sheetName val="U8520 Bugs"/>
@@ -2059,8 +1442,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="VZW BREW Data Sheet "/>
       <sheetName val="OEM Master"/>
@@ -2096,8 +1482,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Weekly Cases Opened"/>
       <sheetName val="核銷表"/>
@@ -2123,8 +1512,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Assumptions_Conditions"/>
       <sheetName val="Organization"/>
@@ -2148,8 +1540,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="risktemp"/>
       <sheetName val="risktemp.xls"/>
@@ -2181,8 +1576,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cover"/>
       <sheetName val="Orange Features"/>
@@ -2196,8 +1594,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Revision History"/>
       <sheetName val="Test Plan Development"/>
@@ -2219,8 +1620,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="summary, MTH"/>
       <sheetName val="summary_ MTH"/>
@@ -2242,8 +1646,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Vertical Schedule guidance"/>
       <sheetName val="Sheet1"/>
@@ -2541,165 +1948,165 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:AB31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AB29"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.070796460177" style="1" customWidth="1"/>
-    <col min="2" max="2" width="35.4690265486726" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.3362831858407" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.20353982300885" style="1" customWidth="1"/>
-    <col min="5" max="6" width="5.60176991150442" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15" style="1" customWidth="1"/>
+    <col min="2" max="2" width="35.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="6.1640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="5.6640625" style="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.3362831858407" style="1" customWidth="1"/>
-    <col min="9" max="10" width="5.79646017699115" style="1" customWidth="1"/>
-    <col min="11" max="11" width="5.92920353982301" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.3362831858407" style="1" customWidth="1"/>
-    <col min="13" max="15" width="5.60176991150442" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9.33628318584071" style="1" customWidth="1"/>
-    <col min="17" max="20" width="5.60176991150442" style="1" customWidth="1"/>
-    <col min="21" max="21" width="9.33628318584071" style="1" customWidth="1"/>
-    <col min="22" max="24" width="5.60176991150442" style="1" customWidth="1"/>
-    <col min="25" max="25" width="9.33628318584071" style="1" customWidth="1"/>
-    <col min="26" max="27" width="5.60176991150442" style="1" customWidth="1"/>
-    <col min="28" max="28" width="9.20353982300885" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" style="1" customWidth="1"/>
+    <col min="9" max="10" width="5.83203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="6" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.33203125" style="1" customWidth="1"/>
+    <col min="13" max="15" width="5.6640625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9.33203125" style="1" customWidth="1"/>
+    <col min="17" max="20" width="5.6640625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="9.33203125" style="1" customWidth="1"/>
+    <col min="22" max="24" width="5.6640625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="9.33203125" style="1" customWidth="1"/>
+    <col min="26" max="27" width="5.6640625" style="1" customWidth="1"/>
+    <col min="28" max="28" width="9.1640625" style="1" customWidth="1"/>
     <col min="29" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" spans="1:28">
+    <row r="1" spans="1:28" ht="15" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3">
+      <c r="C1" s="29">
         <v>46023</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="6">
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="32">
         <v>46054</v>
       </c>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="9">
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="35">
         <v>46082</v>
       </c>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="12">
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="38">
         <v>46113</v>
       </c>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="15">
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="41">
         <v>46143</v>
       </c>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16"/>
-      <c r="W1" s="16"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="18">
+      <c r="U1" s="42"/>
+      <c r="V1" s="42"/>
+      <c r="W1" s="42"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="26">
         <v>46174</v>
       </c>
-      <c r="Z1" s="19"/>
-      <c r="AA1" s="19"/>
-      <c r="AB1" s="20"/>
+      <c r="Z1" s="27"/>
+      <c r="AA1" s="27"/>
+      <c r="AB1" s="28"/>
     </row>
     <row r="2" spans="1:28">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="23">
+      <c r="C2" s="5">
         <v>46027</v>
       </c>
-      <c r="D2" s="23">
+      <c r="D2" s="5">
         <v>46034</v>
       </c>
-      <c r="E2" s="23">
+      <c r="E2" s="5">
         <v>46041</v>
       </c>
-      <c r="F2" s="23">
+      <c r="F2" s="5">
         <v>46048</v>
       </c>
-      <c r="G2" s="23">
+      <c r="G2" s="5">
         <v>46055</v>
       </c>
-      <c r="H2" s="23">
+      <c r="H2" s="5">
         <v>46062</v>
       </c>
-      <c r="I2" s="24">
+      <c r="I2" s="5">
         <v>46069</v>
       </c>
-      <c r="J2" s="25">
+      <c r="J2" s="6">
         <v>46076</v>
       </c>
-      <c r="K2" s="26">
+      <c r="K2" s="7">
         <v>46083</v>
       </c>
-      <c r="L2" s="27">
+      <c r="L2" s="8">
         <v>46090</v>
       </c>
-      <c r="M2" s="23">
+      <c r="M2" s="5">
         <v>46097</v>
       </c>
-      <c r="N2" s="23">
+      <c r="N2" s="5">
         <v>46104</v>
       </c>
-      <c r="O2" s="23">
+      <c r="O2" s="5">
         <v>46111</v>
       </c>
-      <c r="P2" s="23">
+      <c r="P2" s="5">
         <v>46118</v>
       </c>
-      <c r="Q2" s="23">
+      <c r="Q2" s="5">
         <v>46125</v>
       </c>
-      <c r="R2" s="23">
+      <c r="R2" s="5">
         <v>46132</v>
       </c>
-      <c r="S2" s="23">
+      <c r="S2" s="5">
         <v>46139</v>
       </c>
-      <c r="T2" s="26">
+      <c r="T2" s="7">
         <v>46146</v>
       </c>
-      <c r="U2" s="27">
+      <c r="U2" s="8">
         <v>46153</v>
       </c>
-      <c r="V2" s="23">
+      <c r="V2" s="5">
         <v>46160</v>
       </c>
-      <c r="W2" s="23">
+      <c r="W2" s="5">
         <v>46167</v>
       </c>
-      <c r="X2" s="23">
+      <c r="X2" s="5">
         <v>46174</v>
       </c>
-      <c r="Y2" s="23">
+      <c r="Y2" s="5">
         <v>46181</v>
       </c>
-      <c r="Z2" s="23">
+      <c r="Z2" s="5">
         <v>46188</v>
       </c>
-      <c r="AA2" s="23">
+      <c r="AA2" s="5">
         <v>46195</v>
       </c>
-      <c r="AB2" s="23">
+      <c r="AB2" s="5">
         <v>46202</v>
       </c>
     </row>
@@ -2707,2316 +2114,2234 @@
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="E3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="29" t="s">
+      <c r="G3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="29" t="s">
+      <c r="H3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="30" t="s">
+      <c r="I3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="31" t="s">
+      <c r="J3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="K3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="32" t="s">
+      <c r="L3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="32" t="s">
+      <c r="M3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="32" t="s">
+      <c r="N3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="32" t="s">
+      <c r="O3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="P3" s="32" t="s">
+      <c r="P3" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="32" t="s">
+      <c r="Q3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="32" t="s">
+      <c r="R3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="S3" s="32" t="s">
+      <c r="S3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="T3" s="32" t="s">
+      <c r="T3" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="U3" s="32" t="s">
+      <c r="U3" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="V3" s="32" t="s">
+      <c r="V3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="W3" s="32" t="s">
+      <c r="W3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="X3" s="32" t="s">
+      <c r="X3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="Y3" s="32" t="s">
+      <c r="Y3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="Z3" s="32" t="s">
+      <c r="Z3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="AA3" s="32" t="s">
+      <c r="AA3" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="AB3" s="32" t="s">
+      <c r="AB3" s="12" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:28">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="34">
-        <v>0</v>
-      </c>
-      <c r="D4" s="34">
-        <v>0</v>
-      </c>
-      <c r="E4" s="34">
+      <c r="C4" s="14">
+        <v>0</v>
+      </c>
+      <c r="D4" s="14">
+        <v>0</v>
+      </c>
+      <c r="E4" s="14">
         <v>6</v>
       </c>
-      <c r="F4" s="34">
+      <c r="F4" s="14">
         <v>5</v>
       </c>
-      <c r="G4" s="34">
+      <c r="G4" s="14">
         <v>5</v>
       </c>
-      <c r="H4" s="34">
+      <c r="H4" s="14">
         <v>4</v>
       </c>
-      <c r="I4" s="35">
-        <v>0</v>
-      </c>
-      <c r="J4" s="34">
+      <c r="I4" s="14">
+        <v>0</v>
+      </c>
+      <c r="J4" s="14">
         <v>3</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="14">
         <v>2</v>
       </c>
-      <c r="L4" s="34">
-        <v>1</v>
-      </c>
-      <c r="M4" s="34">
-        <v>0</v>
-      </c>
-      <c r="N4" s="34">
-        <v>0</v>
-      </c>
-      <c r="O4" s="34">
-        <v>0</v>
-      </c>
-      <c r="P4" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="34">
-        <v>0</v>
-      </c>
-      <c r="R4" s="36">
-        <v>1</v>
-      </c>
-      <c r="S4" s="34">
-        <v>0</v>
-      </c>
-      <c r="T4" s="34">
-        <v>0</v>
-      </c>
-      <c r="U4" s="34">
-        <v>1</v>
-      </c>
-      <c r="V4" s="34">
-        <v>0</v>
-      </c>
-      <c r="W4" s="34">
-        <v>0</v>
-      </c>
-      <c r="X4" s="34">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="34">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="34">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="34">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="34">
+      <c r="L4" s="14">
+        <v>1</v>
+      </c>
+      <c r="M4" s="14">
+        <v>0</v>
+      </c>
+      <c r="N4" s="14">
+        <v>0</v>
+      </c>
+      <c r="O4" s="14">
+        <v>0</v>
+      </c>
+      <c r="P4" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="14">
+        <v>0</v>
+      </c>
+      <c r="R4" s="14">
+        <v>1</v>
+      </c>
+      <c r="S4" s="14">
+        <v>0</v>
+      </c>
+      <c r="T4" s="14">
+        <v>0</v>
+      </c>
+      <c r="U4" s="14">
+        <v>1</v>
+      </c>
+      <c r="V4" s="14">
+        <v>0</v>
+      </c>
+      <c r="W4" s="14">
+        <v>0</v>
+      </c>
+      <c r="X4" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="14">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:28">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="34">
-        <v>0</v>
-      </c>
-      <c r="D5" s="34">
-        <v>0</v>
-      </c>
-      <c r="E5" s="34">
+      <c r="C5" s="14">
+        <v>0</v>
+      </c>
+      <c r="D5" s="14">
+        <v>0</v>
+      </c>
+      <c r="E5" s="14">
         <v>4</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="14">
         <v>75</v>
       </c>
-      <c r="G5" s="34">
+      <c r="G5" s="14">
         <v>84</v>
       </c>
-      <c r="H5" s="34">
+      <c r="H5" s="14">
         <v>77</v>
       </c>
-      <c r="I5" s="35">
-        <v>0</v>
-      </c>
-      <c r="J5" s="34">
+      <c r="I5" s="14">
+        <v>0</v>
+      </c>
+      <c r="J5" s="14">
         <v>64</v>
       </c>
-      <c r="K5" s="34">
+      <c r="K5" s="14">
         <v>52</v>
       </c>
-      <c r="L5" s="34">
+      <c r="L5" s="14">
         <v>38</v>
       </c>
-      <c r="M5" s="34">
+      <c r="M5" s="14">
         <v>19</v>
       </c>
-      <c r="N5" s="34">
+      <c r="N5" s="14">
         <v>15</v>
       </c>
-      <c r="O5" s="34">
+      <c r="O5" s="14">
         <v>11</v>
       </c>
-      <c r="P5" s="34">
+      <c r="P5" s="14">
         <v>5</v>
       </c>
-      <c r="Q5" s="34">
+      <c r="Q5" s="14">
         <v>4</v>
       </c>
-      <c r="R5" s="36">
+      <c r="R5" s="14">
         <v>2</v>
       </c>
-      <c r="S5" s="34">
+      <c r="S5" s="14">
         <v>2</v>
       </c>
-      <c r="T5" s="34">
-        <v>1</v>
-      </c>
-      <c r="U5" s="34">
-        <v>1</v>
-      </c>
-      <c r="V5" s="34">
-        <v>1</v>
-      </c>
-      <c r="W5" s="34">
-        <v>0</v>
-      </c>
-      <c r="X5" s="34">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="34">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="34">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="34">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="34">
+      <c r="T5" s="14">
+        <v>1</v>
+      </c>
+      <c r="U5" s="14">
+        <v>1</v>
+      </c>
+      <c r="V5" s="14">
+        <v>1</v>
+      </c>
+      <c r="W5" s="14">
+        <v>0</v>
+      </c>
+      <c r="X5" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="14">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:28">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="34">
-        <v>0</v>
-      </c>
-      <c r="D6" s="34">
-        <v>0</v>
-      </c>
-      <c r="E6" s="34">
+      <c r="C6" s="14">
+        <v>0</v>
+      </c>
+      <c r="D6" s="14">
+        <v>0</v>
+      </c>
+      <c r="E6" s="14">
         <v>2</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="14">
         <v>5</v>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="14">
         <v>8</v>
       </c>
-      <c r="H6" s="34">
+      <c r="H6" s="14">
         <v>6</v>
       </c>
-      <c r="I6" s="35">
-        <v>0</v>
-      </c>
-      <c r="J6" s="34">
+      <c r="I6" s="14">
+        <v>0</v>
+      </c>
+      <c r="J6" s="14">
         <v>4</v>
       </c>
-      <c r="K6" s="34">
+      <c r="K6" s="14">
         <v>2</v>
       </c>
-      <c r="L6" s="34">
+      <c r="L6" s="14">
         <v>2</v>
       </c>
-      <c r="M6" s="34">
-        <v>1</v>
-      </c>
-      <c r="N6" s="34">
-        <v>1</v>
-      </c>
-      <c r="O6" s="34">
-        <v>0</v>
-      </c>
-      <c r="P6" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="34">
-        <v>0</v>
-      </c>
-      <c r="R6" s="36">
-        <v>0</v>
-      </c>
-      <c r="S6" s="34">
-        <v>0</v>
-      </c>
-      <c r="T6" s="34">
-        <v>0</v>
-      </c>
-      <c r="U6" s="34">
-        <v>0</v>
-      </c>
-      <c r="V6" s="34">
-        <v>0</v>
-      </c>
-      <c r="W6" s="34">
-        <v>0</v>
-      </c>
-      <c r="X6" s="34">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="34">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="34">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="34">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="34">
+      <c r="M6" s="14">
+        <v>1</v>
+      </c>
+      <c r="N6" s="14">
+        <v>1</v>
+      </c>
+      <c r="O6" s="14">
+        <v>0</v>
+      </c>
+      <c r="P6" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="14">
+        <v>0</v>
+      </c>
+      <c r="R6" s="14">
+        <v>0</v>
+      </c>
+      <c r="S6" s="14">
+        <v>0</v>
+      </c>
+      <c r="T6" s="14">
+        <v>0</v>
+      </c>
+      <c r="U6" s="14">
+        <v>0</v>
+      </c>
+      <c r="V6" s="14">
+        <v>0</v>
+      </c>
+      <c r="W6" s="14">
+        <v>0</v>
+      </c>
+      <c r="X6" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="14">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:28">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="34">
-        <v>0</v>
-      </c>
-      <c r="D7" s="34">
-        <v>0</v>
-      </c>
-      <c r="E7" s="34">
+      <c r="C7" s="14">
+        <v>0</v>
+      </c>
+      <c r="D7" s="14">
+        <v>0</v>
+      </c>
+      <c r="E7" s="14">
         <v>3</v>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="14">
         <v>32</v>
       </c>
-      <c r="G7" s="34">
+      <c r="G7" s="14">
         <v>42</v>
       </c>
-      <c r="H7" s="34">
+      <c r="H7" s="14">
         <v>36</v>
       </c>
-      <c r="I7" s="35">
-        <v>0</v>
-      </c>
-      <c r="J7" s="34">
+      <c r="I7" s="14">
+        <v>0</v>
+      </c>
+      <c r="J7" s="14">
         <v>7</v>
       </c>
-      <c r="K7" s="34">
+      <c r="K7" s="14">
         <v>6</v>
       </c>
-      <c r="L7" s="34">
+      <c r="L7" s="14">
         <v>3</v>
       </c>
-      <c r="M7" s="34">
+      <c r="M7" s="14">
         <v>2</v>
       </c>
-      <c r="N7" s="34">
-        <v>0</v>
-      </c>
-      <c r="O7" s="34">
-        <v>0</v>
-      </c>
-      <c r="P7" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="34">
-        <v>0</v>
-      </c>
-      <c r="R7" s="34">
-        <v>0</v>
-      </c>
-      <c r="S7" s="34">
-        <v>0</v>
-      </c>
-      <c r="T7" s="34">
-        <v>0</v>
-      </c>
-      <c r="U7" s="34">
-        <v>0</v>
-      </c>
-      <c r="V7" s="34">
-        <v>0</v>
-      </c>
-      <c r="W7" s="34">
-        <v>0</v>
-      </c>
-      <c r="X7" s="34">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="34">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="34">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="34">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="34">
+      <c r="N7" s="14">
+        <v>0</v>
+      </c>
+      <c r="O7" s="14">
+        <v>0</v>
+      </c>
+      <c r="P7" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="14">
+        <v>0</v>
+      </c>
+      <c r="R7" s="14">
+        <v>0</v>
+      </c>
+      <c r="S7" s="14">
+        <v>0</v>
+      </c>
+      <c r="T7" s="14">
+        <v>0</v>
+      </c>
+      <c r="U7" s="14">
+        <v>0</v>
+      </c>
+      <c r="V7" s="14">
+        <v>0</v>
+      </c>
+      <c r="W7" s="14">
+        <v>0</v>
+      </c>
+      <c r="X7" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="14">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:28">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="34">
-        <v>0</v>
-      </c>
-      <c r="D8" s="34">
-        <v>0</v>
-      </c>
-      <c r="E8" s="34">
-        <v>0</v>
-      </c>
-      <c r="F8" s="34">
-        <v>0</v>
-      </c>
-      <c r="G8" s="34">
+      <c r="C8" s="14">
+        <v>0</v>
+      </c>
+      <c r="D8" s="14">
+        <v>0</v>
+      </c>
+      <c r="E8" s="14">
+        <v>0</v>
+      </c>
+      <c r="F8" s="14">
+        <v>0</v>
+      </c>
+      <c r="G8" s="14">
         <v>22</v>
       </c>
-      <c r="H8" s="34">
+      <c r="H8" s="14">
         <v>26</v>
       </c>
-      <c r="I8" s="35">
-        <v>0</v>
-      </c>
-      <c r="J8" s="34">
+      <c r="I8" s="14">
+        <v>0</v>
+      </c>
+      <c r="J8" s="14">
         <v>4</v>
       </c>
-      <c r="K8" s="34">
-        <v>1</v>
-      </c>
-      <c r="L8" s="34">
-        <v>1</v>
-      </c>
-      <c r="M8" s="34">
-        <v>0</v>
-      </c>
-      <c r="N8" s="34">
-        <v>0</v>
-      </c>
-      <c r="O8" s="34">
-        <v>0</v>
-      </c>
-      <c r="P8" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="34">
-        <v>0</v>
-      </c>
-      <c r="R8" s="34">
-        <v>0</v>
-      </c>
-      <c r="S8" s="34">
-        <v>0</v>
-      </c>
-      <c r="T8" s="34">
-        <v>0</v>
-      </c>
-      <c r="U8" s="34">
-        <v>0</v>
-      </c>
-      <c r="V8" s="34">
-        <v>0</v>
-      </c>
-      <c r="W8" s="34">
-        <v>0</v>
-      </c>
-      <c r="X8" s="34">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="34">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="34">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="34">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="34">
+      <c r="K8" s="14">
+        <v>1</v>
+      </c>
+      <c r="L8" s="14">
+        <v>1</v>
+      </c>
+      <c r="M8" s="14">
+        <v>0</v>
+      </c>
+      <c r="N8" s="14">
+        <v>0</v>
+      </c>
+      <c r="O8" s="14">
+        <v>0</v>
+      </c>
+      <c r="P8" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="14">
+        <v>0</v>
+      </c>
+      <c r="R8" s="14">
+        <v>0</v>
+      </c>
+      <c r="S8" s="14">
+        <v>0</v>
+      </c>
+      <c r="T8" s="14">
+        <v>0</v>
+      </c>
+      <c r="U8" s="14">
+        <v>0</v>
+      </c>
+      <c r="V8" s="14">
+        <v>0</v>
+      </c>
+      <c r="W8" s="14">
+        <v>0</v>
+      </c>
+      <c r="X8" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="14">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:28">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="34">
-        <v>0</v>
-      </c>
-      <c r="D9" s="34">
+      <c r="C9" s="14">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14">
         <v>2</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="14">
         <v>5</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="14">
         <v>41</v>
       </c>
-      <c r="G9" s="34">
+      <c r="G9" s="14">
         <v>58</v>
       </c>
-      <c r="H9" s="34">
+      <c r="H9" s="14">
         <v>56</v>
       </c>
-      <c r="I9" s="35">
+      <c r="I9" s="14">
         <v>35</v>
       </c>
-      <c r="J9" s="34">
+      <c r="J9" s="14">
         <v>37</v>
       </c>
-      <c r="K9" s="34">
+      <c r="K9" s="14">
         <v>21</v>
       </c>
-      <c r="L9" s="34">
+      <c r="L9" s="14">
         <v>10</v>
       </c>
-      <c r="M9" s="34">
+      <c r="M9" s="14">
         <v>5</v>
       </c>
-      <c r="N9" s="34">
-        <v>1</v>
-      </c>
-      <c r="O9" s="34">
-        <v>1</v>
-      </c>
-      <c r="P9" s="34">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="34">
-        <v>1</v>
-      </c>
-      <c r="R9" s="36">
-        <v>1</v>
-      </c>
-      <c r="S9" s="34">
-        <v>0</v>
-      </c>
-      <c r="T9" s="34">
-        <v>0</v>
-      </c>
-      <c r="U9" s="34">
-        <v>0</v>
-      </c>
-      <c r="V9" s="34">
-        <v>0</v>
-      </c>
-      <c r="W9" s="34">
-        <v>0</v>
-      </c>
-      <c r="X9" s="34">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="34">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="34">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="34">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="34">
+      <c r="N9" s="14">
+        <v>1</v>
+      </c>
+      <c r="O9" s="14">
+        <v>1</v>
+      </c>
+      <c r="P9" s="14">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="14">
+        <v>1</v>
+      </c>
+      <c r="R9" s="14">
+        <v>1</v>
+      </c>
+      <c r="S9" s="14">
+        <v>0</v>
+      </c>
+      <c r="T9" s="14">
+        <v>0</v>
+      </c>
+      <c r="U9" s="14">
+        <v>0</v>
+      </c>
+      <c r="V9" s="14">
+        <v>0</v>
+      </c>
+      <c r="W9" s="14">
+        <v>0</v>
+      </c>
+      <c r="X9" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:28">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="34">
-        <v>0</v>
-      </c>
-      <c r="D10" s="34">
-        <v>0</v>
-      </c>
-      <c r="E10" s="34">
-        <v>1</v>
-      </c>
-      <c r="F10" s="34">
-        <v>0</v>
-      </c>
-      <c r="G10" s="34">
-        <v>0</v>
-      </c>
-      <c r="H10" s="34">
-        <v>0</v>
-      </c>
-      <c r="I10" s="35">
-        <v>0</v>
-      </c>
-      <c r="J10" s="34">
-        <v>1</v>
-      </c>
-      <c r="K10" s="34">
-        <v>0</v>
-      </c>
-      <c r="L10" s="34">
-        <v>0</v>
-      </c>
-      <c r="M10" s="34">
-        <v>0</v>
-      </c>
-      <c r="N10" s="34">
-        <v>0</v>
-      </c>
-      <c r="O10" s="34">
-        <v>0</v>
-      </c>
-      <c r="P10" s="34">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="34">
-        <v>0</v>
-      </c>
-      <c r="R10" s="34">
-        <v>0</v>
-      </c>
-      <c r="S10" s="34">
-        <v>0</v>
-      </c>
-      <c r="T10" s="34">
-        <v>0</v>
-      </c>
-      <c r="U10" s="34">
-        <v>0</v>
-      </c>
-      <c r="V10" s="34">
-        <v>0</v>
-      </c>
-      <c r="W10" s="34">
-        <v>0</v>
-      </c>
-      <c r="X10" s="34">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="34">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="34">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="34">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="34">
+      <c r="C10" s="14">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14">
+        <v>0</v>
+      </c>
+      <c r="E10" s="14">
+        <v>1</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>0</v>
+      </c>
+      <c r="I10" s="14">
+        <v>0</v>
+      </c>
+      <c r="J10" s="14">
+        <v>1</v>
+      </c>
+      <c r="K10" s="14">
+        <v>0</v>
+      </c>
+      <c r="L10" s="14">
+        <v>0</v>
+      </c>
+      <c r="M10" s="14">
+        <v>0</v>
+      </c>
+      <c r="N10" s="14">
+        <v>0</v>
+      </c>
+      <c r="O10" s="14">
+        <v>0</v>
+      </c>
+      <c r="P10" s="14">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="14">
+        <v>0</v>
+      </c>
+      <c r="R10" s="14">
+        <v>0</v>
+      </c>
+      <c r="S10" s="14">
+        <v>0</v>
+      </c>
+      <c r="T10" s="14">
+        <v>0</v>
+      </c>
+      <c r="U10" s="14">
+        <v>0</v>
+      </c>
+      <c r="V10" s="14">
+        <v>0</v>
+      </c>
+      <c r="W10" s="14">
+        <v>0</v>
+      </c>
+      <c r="X10" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="14">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:28">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="34">
-        <v>0</v>
-      </c>
-      <c r="D11" s="34">
-        <v>0</v>
-      </c>
-      <c r="E11" s="34">
-        <v>0</v>
-      </c>
-      <c r="F11" s="34">
-        <v>0</v>
-      </c>
-      <c r="G11" s="34">
-        <v>1</v>
-      </c>
-      <c r="H11" s="34">
-        <v>1</v>
-      </c>
-      <c r="I11" s="35">
-        <v>0</v>
-      </c>
-      <c r="J11" s="34">
-        <v>1</v>
-      </c>
-      <c r="K11" s="34">
-        <v>0</v>
-      </c>
-      <c r="L11" s="34">
-        <v>0</v>
-      </c>
-      <c r="M11" s="34">
-        <v>0</v>
-      </c>
-      <c r="N11" s="34">
-        <v>0</v>
-      </c>
-      <c r="O11" s="34">
-        <v>0</v>
-      </c>
-      <c r="P11" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="34">
-        <v>0</v>
-      </c>
-      <c r="R11" s="34">
-        <v>0</v>
-      </c>
-      <c r="S11" s="34">
-        <v>0</v>
-      </c>
-      <c r="T11" s="34">
-        <v>0</v>
-      </c>
-      <c r="U11" s="34">
-        <v>0</v>
-      </c>
-      <c r="V11" s="34">
-        <v>0</v>
-      </c>
-      <c r="W11" s="34">
-        <v>0</v>
-      </c>
-      <c r="X11" s="34">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="34">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="34">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="34">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="34">
+      <c r="C11" s="14">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14">
+        <v>0</v>
+      </c>
+      <c r="E11" s="14">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>1</v>
+      </c>
+      <c r="H11" s="14">
+        <v>1</v>
+      </c>
+      <c r="I11" s="14">
+        <v>0</v>
+      </c>
+      <c r="J11" s="14">
+        <v>1</v>
+      </c>
+      <c r="K11" s="14">
+        <v>0</v>
+      </c>
+      <c r="L11" s="14">
+        <v>0</v>
+      </c>
+      <c r="M11" s="14">
+        <v>0</v>
+      </c>
+      <c r="N11" s="14">
+        <v>0</v>
+      </c>
+      <c r="O11" s="14">
+        <v>0</v>
+      </c>
+      <c r="P11" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="14">
+        <v>0</v>
+      </c>
+      <c r="R11" s="14">
+        <v>0</v>
+      </c>
+      <c r="S11" s="14">
+        <v>0</v>
+      </c>
+      <c r="T11" s="14">
+        <v>0</v>
+      </c>
+      <c r="U11" s="14">
+        <v>0</v>
+      </c>
+      <c r="V11" s="14">
+        <v>0</v>
+      </c>
+      <c r="W11" s="14">
+        <v>0</v>
+      </c>
+      <c r="X11" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="14">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:28">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="40">
+      <c r="C12" s="18">
         <f>SUM(C3:C11)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="18">
         <f>SUM(D3:D11)</f>
         <v>2</v>
       </c>
-      <c r="E12" s="40">
+      <c r="E12" s="18">
         <f>SUM(E3:E11)</f>
         <v>21</v>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="18">
         <f>SUM(F3:F10)</f>
         <v>158</v>
       </c>
-      <c r="G12" s="40">
+      <c r="G12" s="18">
         <f t="shared" ref="G12:AB12" si="0">SUM(G3:G11)</f>
         <v>220</v>
       </c>
-      <c r="H12" s="40">
+      <c r="H12" s="18">
         <f t="shared" si="0"/>
         <v>206</v>
       </c>
-      <c r="I12" s="41">
+      <c r="I12" s="18">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="J12" s="40">
+      <c r="J12" s="18">
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
-      <c r="K12" s="40">
+      <c r="K12" s="18">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="L12" s="40">
+      <c r="L12" s="18">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="M12" s="40">
+      <c r="M12" s="18">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="N12" s="40">
+      <c r="N12" s="18">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="O12" s="40">
+      <c r="O12" s="18">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="P12" s="40">
+      <c r="P12" s="18">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="Q12" s="40">
+      <c r="Q12" s="18">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="R12" s="40">
+      <c r="R12" s="18">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="S12" s="40">
+      <c r="S12" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="T12" s="40">
+      <c r="T12" s="18">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U12" s="40">
+      <c r="U12" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="V12" s="40">
+      <c r="V12" s="18">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="W12" s="40">
+      <c r="W12" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X12" s="40">
+      <c r="X12" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y12" s="40">
+      <c r="Y12" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Z12" s="40">
+      <c r="Z12" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA12" s="40">
+      <c r="AA12" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AB12" s="40">
+      <c r="AB12" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:28">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="43">
+      <c r="C13" s="20">
         <f>C12</f>
         <v>0</v>
       </c>
-      <c r="D13" s="43">
+      <c r="D13" s="20">
         <f>C13+D12</f>
         <v>2</v>
       </c>
-      <c r="E13" s="43">
+      <c r="E13" s="20">
         <f>D13+E12</f>
         <v>23</v>
       </c>
-      <c r="F13" s="43">
+      <c r="F13" s="20">
         <f t="shared" ref="F13:U13" si="1">E13+F12</f>
         <v>181</v>
       </c>
-      <c r="G13" s="43">
+      <c r="G13" s="20">
         <f t="shared" si="1"/>
         <v>401</v>
       </c>
-      <c r="H13" s="43">
+      <c r="H13" s="20">
         <f t="shared" si="1"/>
         <v>607</v>
       </c>
-      <c r="I13" s="41">
+      <c r="I13" s="20">
         <f t="shared" si="1"/>
         <v>642</v>
       </c>
-      <c r="J13" s="43">
+      <c r="J13" s="20">
         <f t="shared" si="1"/>
         <v>763</v>
       </c>
-      <c r="K13" s="43">
+      <c r="K13" s="20">
         <f t="shared" si="1"/>
         <v>847</v>
       </c>
-      <c r="L13" s="43">
+      <c r="L13" s="20">
         <f t="shared" si="1"/>
         <v>902</v>
       </c>
-      <c r="M13" s="43">
+      <c r="M13" s="20">
         <f t="shared" si="1"/>
         <v>929</v>
       </c>
-      <c r="N13" s="43">
+      <c r="N13" s="20">
         <f t="shared" si="1"/>
         <v>946</v>
       </c>
-      <c r="O13" s="44">
+      <c r="O13" s="21">
         <f t="shared" si="1"/>
         <v>958</v>
       </c>
-      <c r="P13" s="43">
+      <c r="P13" s="20">
         <f t="shared" si="1"/>
         <v>965</v>
       </c>
-      <c r="Q13" s="44">
+      <c r="Q13" s="21">
         <f t="shared" si="1"/>
         <v>970</v>
       </c>
-      <c r="R13" s="44">
+      <c r="R13" s="21">
         <f t="shared" si="1"/>
         <v>974</v>
       </c>
-      <c r="S13" s="43">
+      <c r="S13" s="20">
         <f t="shared" si="1"/>
         <v>976</v>
       </c>
-      <c r="T13" s="43">
+      <c r="T13" s="20">
         <f t="shared" si="1"/>
         <v>977</v>
       </c>
-      <c r="U13" s="43">
+      <c r="U13" s="20">
         <f t="shared" si="1"/>
         <v>979</v>
       </c>
-      <c r="V13" s="43">
+      <c r="V13" s="20">
         <f t="shared" ref="V13" si="2">U13+V12</f>
         <v>980</v>
       </c>
-      <c r="W13" s="43">
+      <c r="W13" s="20">
         <f t="shared" ref="W13" si="3">V13+W12</f>
         <v>980</v>
       </c>
-      <c r="X13" s="43">
+      <c r="X13" s="20">
         <f t="shared" ref="X13" si="4">W13+X12</f>
         <v>980</v>
       </c>
-      <c r="Y13" s="43">
+      <c r="Y13" s="20">
         <f t="shared" ref="Y13" si="5">X13+Y12</f>
         <v>980</v>
       </c>
-      <c r="Z13" s="43">
+      <c r="Z13" s="20">
         <f t="shared" ref="Z13" si="6">Y13+Z12</f>
         <v>980</v>
       </c>
-      <c r="AA13" s="43">
+      <c r="AA13" s="20">
         <f t="shared" ref="AA13" si="7">Z13+AA12</f>
         <v>980</v>
       </c>
-      <c r="AB13" s="43">
+      <c r="AB13" s="20">
         <f t="shared" ref="AB13" si="8">AA13+AB12</f>
         <v>980</v>
       </c>
     </row>
     <row r="14" spans="1:28">
-      <c r="A14" s="33" t="s">
+      <c r="A14" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="45">
-        <v>0</v>
-      </c>
-      <c r="D14" s="45">
-        <v>0</v>
-      </c>
-      <c r="E14" s="45">
-        <v>1</v>
-      </c>
-      <c r="F14" s="45">
+      <c r="C14" s="22">
+        <v>0</v>
+      </c>
+      <c r="D14" s="22">
+        <v>0</v>
+      </c>
+      <c r="E14" s="22">
+        <v>1</v>
+      </c>
+      <c r="F14" s="22">
         <v>8</v>
       </c>
-      <c r="G14" s="45">
+      <c r="G14" s="22">
         <v>12</v>
       </c>
-      <c r="H14" s="45">
+      <c r="H14" s="22">
         <v>23</v>
       </c>
-      <c r="I14" s="46">
+      <c r="I14" s="14">
         <v>3</v>
       </c>
-      <c r="J14" s="45">
+      <c r="J14" s="22">
         <v>28</v>
       </c>
-      <c r="K14" s="45">
+      <c r="K14" s="22">
         <v>20</v>
       </c>
-      <c r="L14" s="45">
+      <c r="L14" s="22">
         <v>15</v>
       </c>
-      <c r="M14" s="45">
+      <c r="M14" s="22">
         <v>13</v>
       </c>
-      <c r="N14" s="45">
+      <c r="N14" s="22">
         <v>8</v>
       </c>
-      <c r="O14" s="45">
+      <c r="O14" s="22">
         <v>2</v>
       </c>
-      <c r="P14" s="45">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="45">
-        <v>1</v>
-      </c>
-      <c r="R14" s="47">
-        <v>1</v>
-      </c>
-      <c r="S14" s="45">
-        <v>1</v>
-      </c>
-      <c r="T14" s="45">
-        <v>1</v>
-      </c>
-      <c r="U14" s="45">
-        <v>1</v>
-      </c>
-      <c r="V14" s="45">
-        <v>1</v>
-      </c>
-      <c r="W14" s="45">
-        <v>0</v>
-      </c>
-      <c r="X14" s="45">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="45">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="45">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="45">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="45">
+      <c r="P14" s="22">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
+      <c r="R14" s="22">
+        <v>1</v>
+      </c>
+      <c r="S14" s="22">
+        <v>1</v>
+      </c>
+      <c r="T14" s="22">
+        <v>1</v>
+      </c>
+      <c r="U14" s="22">
+        <v>1</v>
+      </c>
+      <c r="V14" s="22">
+        <v>1</v>
+      </c>
+      <c r="W14" s="22">
+        <v>0</v>
+      </c>
+      <c r="X14" s="22">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="22">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="22">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:28">
-      <c r="A15" s="33" t="s">
+      <c r="A15" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="45">
-        <v>0</v>
-      </c>
-      <c r="D15" s="45">
-        <v>0</v>
-      </c>
-      <c r="E15" s="45">
-        <v>1</v>
-      </c>
-      <c r="F15" s="45">
+      <c r="C15" s="22">
+        <v>0</v>
+      </c>
+      <c r="D15" s="22">
+        <v>0</v>
+      </c>
+      <c r="E15" s="22">
+        <v>1</v>
+      </c>
+      <c r="F15" s="22">
         <v>8</v>
       </c>
-      <c r="G15" s="45">
+      <c r="G15" s="22">
         <v>12</v>
       </c>
-      <c r="H15" s="45">
+      <c r="H15" s="22">
         <v>15</v>
       </c>
-      <c r="I15" s="46">
-        <v>0</v>
-      </c>
-      <c r="J15" s="45">
+      <c r="I15" s="14">
+        <v>0</v>
+      </c>
+      <c r="J15" s="22">
         <v>19</v>
       </c>
-      <c r="K15" s="45">
+      <c r="K15" s="22">
         <v>13</v>
       </c>
-      <c r="L15" s="45">
+      <c r="L15" s="22">
         <v>6</v>
       </c>
-      <c r="M15" s="45">
+      <c r="M15" s="22">
         <v>4</v>
       </c>
-      <c r="N15" s="45">
+      <c r="N15" s="22">
         <v>3</v>
       </c>
-      <c r="O15" s="45">
-        <v>1</v>
-      </c>
-      <c r="P15" s="45">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="45">
-        <v>0</v>
-      </c>
-      <c r="R15" s="47">
-        <v>0</v>
-      </c>
-      <c r="S15" s="45">
-        <v>0</v>
-      </c>
-      <c r="T15" s="45">
-        <v>0</v>
-      </c>
-      <c r="U15" s="45">
-        <v>0</v>
-      </c>
-      <c r="V15" s="45">
-        <v>0</v>
-      </c>
-      <c r="W15" s="45">
-        <v>0</v>
-      </c>
-      <c r="X15" s="45">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="45">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="45">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="45">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="45">
+      <c r="O15" s="22">
+        <v>1</v>
+      </c>
+      <c r="P15" s="22">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="22">
+        <v>0</v>
+      </c>
+      <c r="R15" s="22">
+        <v>0</v>
+      </c>
+      <c r="S15" s="22">
+        <v>0</v>
+      </c>
+      <c r="T15" s="22">
+        <v>0</v>
+      </c>
+      <c r="U15" s="22">
+        <v>0</v>
+      </c>
+      <c r="V15" s="22">
+        <v>0</v>
+      </c>
+      <c r="W15" s="22">
+        <v>0</v>
+      </c>
+      <c r="X15" s="22">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="22">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="22">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:28">
-      <c r="A16" s="33" t="s">
+      <c r="A16" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="45">
-        <v>0</v>
-      </c>
-      <c r="D16" s="45">
-        <v>0</v>
-      </c>
-      <c r="E16" s="45">
-        <v>1</v>
-      </c>
-      <c r="F16" s="45">
+      <c r="C16" s="22">
+        <v>0</v>
+      </c>
+      <c r="D16" s="22">
+        <v>0</v>
+      </c>
+      <c r="E16" s="22">
+        <v>1</v>
+      </c>
+      <c r="F16" s="22">
         <v>8</v>
       </c>
-      <c r="G16" s="45">
+      <c r="G16" s="22">
         <v>12</v>
       </c>
-      <c r="H16" s="45">
+      <c r="H16" s="22">
         <v>23</v>
       </c>
-      <c r="I16" s="46">
-        <v>0</v>
-      </c>
-      <c r="J16" s="45">
+      <c r="I16" s="14">
+        <v>0</v>
+      </c>
+      <c r="J16" s="22">
         <v>28</v>
       </c>
-      <c r="K16" s="45">
+      <c r="K16" s="22">
         <v>20</v>
       </c>
-      <c r="L16" s="45">
+      <c r="L16" s="22">
         <v>20</v>
       </c>
-      <c r="M16" s="45">
+      <c r="M16" s="22">
         <v>17</v>
       </c>
-      <c r="N16" s="45">
+      <c r="N16" s="22">
         <v>10</v>
       </c>
-      <c r="O16" s="45">
+      <c r="O16" s="22">
         <v>3</v>
       </c>
-      <c r="P16" s="45">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="45">
-        <v>1</v>
-      </c>
-      <c r="R16" s="47">
-        <v>1</v>
-      </c>
-      <c r="S16" s="45">
-        <v>1</v>
-      </c>
-      <c r="T16" s="45">
-        <v>1</v>
-      </c>
-      <c r="U16" s="45">
-        <v>1</v>
-      </c>
-      <c r="V16" s="45">
-        <v>1</v>
-      </c>
-      <c r="W16" s="45">
-        <v>1</v>
-      </c>
-      <c r="X16" s="45">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="45">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="45">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="45">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="45">
+      <c r="P16" s="22">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="22">
+        <v>1</v>
+      </c>
+      <c r="R16" s="22">
+        <v>1</v>
+      </c>
+      <c r="S16" s="22">
+        <v>1</v>
+      </c>
+      <c r="T16" s="22">
+        <v>1</v>
+      </c>
+      <c r="U16" s="22">
+        <v>1</v>
+      </c>
+      <c r="V16" s="22">
+        <v>1</v>
+      </c>
+      <c r="W16" s="22">
+        <v>1</v>
+      </c>
+      <c r="X16" s="22">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="22">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="22">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:28">
-      <c r="A17" s="33" t="s">
+      <c r="A17" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="45">
-        <v>0</v>
-      </c>
-      <c r="D17" s="45">
-        <v>0</v>
-      </c>
-      <c r="E17" s="45">
+      <c r="C17" s="22">
+        <v>0</v>
+      </c>
+      <c r="D17" s="22">
+        <v>0</v>
+      </c>
+      <c r="E17" s="22">
         <v>2</v>
       </c>
-      <c r="F17" s="45">
+      <c r="F17" s="22">
         <v>16</v>
       </c>
-      <c r="G17" s="45">
+      <c r="G17" s="22">
         <v>22</v>
       </c>
-      <c r="H17" s="45">
+      <c r="H17" s="22">
         <v>23</v>
       </c>
-      <c r="I17" s="46">
-        <v>0</v>
-      </c>
-      <c r="J17" s="45">
+      <c r="I17" s="14">
+        <v>0</v>
+      </c>
+      <c r="J17" s="22">
         <v>28</v>
       </c>
-      <c r="K17" s="45">
+      <c r="K17" s="22">
         <v>20</v>
       </c>
-      <c r="L17" s="45">
+      <c r="L17" s="22">
         <v>20</v>
       </c>
-      <c r="M17" s="45">
+      <c r="M17" s="22">
         <v>17</v>
       </c>
-      <c r="N17" s="45">
+      <c r="N17" s="22">
         <v>11</v>
       </c>
-      <c r="O17" s="45">
+      <c r="O17" s="22">
         <v>3</v>
       </c>
-      <c r="P17" s="45">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="45">
-        <v>1</v>
-      </c>
-      <c r="R17" s="47">
-        <v>1</v>
-      </c>
-      <c r="S17" s="45">
-        <v>1</v>
-      </c>
-      <c r="T17" s="45">
-        <v>1</v>
-      </c>
-      <c r="U17" s="45">
-        <v>1</v>
-      </c>
-      <c r="V17" s="45">
-        <v>1</v>
-      </c>
-      <c r="W17" s="45">
-        <v>0</v>
-      </c>
-      <c r="X17" s="45">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="45">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="45">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="45">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="45">
+      <c r="P17" s="22">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="22">
+        <v>1</v>
+      </c>
+      <c r="R17" s="22">
+        <v>1</v>
+      </c>
+      <c r="S17" s="22">
+        <v>1</v>
+      </c>
+      <c r="T17" s="22">
+        <v>1</v>
+      </c>
+      <c r="U17" s="22">
+        <v>1</v>
+      </c>
+      <c r="V17" s="22">
+        <v>1</v>
+      </c>
+      <c r="W17" s="22">
+        <v>0</v>
+      </c>
+      <c r="X17" s="22">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="22">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="22">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:28">
-      <c r="A18" s="33" t="s">
+      <c r="A18" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="45">
-        <v>0</v>
-      </c>
-      <c r="D18" s="45">
-        <v>0</v>
-      </c>
-      <c r="E18" s="45">
+      <c r="C18" s="22">
+        <v>0</v>
+      </c>
+      <c r="D18" s="22">
+        <v>0</v>
+      </c>
+      <c r="E18" s="22">
         <v>3</v>
       </c>
-      <c r="F18" s="45">
+      <c r="F18" s="22">
         <v>23</v>
       </c>
-      <c r="G18" s="45">
+      <c r="G18" s="22">
         <v>34</v>
       </c>
-      <c r="H18" s="45">
+      <c r="H18" s="22">
         <v>30</v>
       </c>
-      <c r="I18" s="46">
-        <v>0</v>
-      </c>
-      <c r="J18" s="45">
+      <c r="I18" s="14">
+        <v>0</v>
+      </c>
+      <c r="J18" s="22">
         <v>37</v>
       </c>
-      <c r="K18" s="45">
+      <c r="K18" s="22">
         <v>26</v>
       </c>
-      <c r="L18" s="45">
+      <c r="L18" s="22">
         <v>15</v>
       </c>
-      <c r="M18" s="45">
+      <c r="M18" s="22">
         <v>13</v>
       </c>
-      <c r="N18" s="45">
+      <c r="N18" s="22">
         <v>8</v>
       </c>
-      <c r="O18" s="45">
+      <c r="O18" s="22">
         <v>2</v>
       </c>
-      <c r="P18" s="45">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="45">
-        <v>1</v>
-      </c>
-      <c r="R18" s="47">
-        <v>1</v>
-      </c>
-      <c r="S18" s="45">
-        <v>1</v>
-      </c>
-      <c r="T18" s="45">
-        <v>1</v>
-      </c>
-      <c r="U18" s="45">
-        <v>1</v>
-      </c>
-      <c r="V18" s="45">
-        <v>0</v>
-      </c>
-      <c r="W18" s="45">
-        <v>0</v>
-      </c>
-      <c r="X18" s="45">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="45">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="45">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="45">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="45">
+      <c r="P18" s="22">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="22">
+        <v>1</v>
+      </c>
+      <c r="R18" s="22">
+        <v>1</v>
+      </c>
+      <c r="S18" s="22">
+        <v>1</v>
+      </c>
+      <c r="T18" s="22">
+        <v>1</v>
+      </c>
+      <c r="U18" s="22">
+        <v>1</v>
+      </c>
+      <c r="V18" s="22">
+        <v>0</v>
+      </c>
+      <c r="W18" s="22">
+        <v>0</v>
+      </c>
+      <c r="X18" s="22">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="22">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="22">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:28">
-      <c r="A19" s="33" t="s">
+      <c r="A19" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="45">
-        <v>0</v>
-      </c>
-      <c r="D19" s="45">
-        <v>0</v>
-      </c>
-      <c r="E19" s="45">
+      <c r="C19" s="22">
+        <v>0</v>
+      </c>
+      <c r="D19" s="22">
+        <v>0</v>
+      </c>
+      <c r="E19" s="22">
         <v>2</v>
       </c>
-      <c r="F19" s="45">
+      <c r="F19" s="22">
         <v>15</v>
       </c>
-      <c r="G19" s="45">
+      <c r="G19" s="22">
         <v>23</v>
       </c>
-      <c r="H19" s="45">
+      <c r="H19" s="22">
         <v>15</v>
       </c>
-      <c r="I19" s="46">
-        <v>0</v>
-      </c>
-      <c r="J19" s="45">
+      <c r="I19" s="14">
+        <v>0</v>
+      </c>
+      <c r="J19" s="22">
         <v>19</v>
       </c>
-      <c r="K19" s="45">
+      <c r="K19" s="22">
         <v>13</v>
       </c>
-      <c r="L19" s="45">
+      <c r="L19" s="22">
         <v>10</v>
       </c>
-      <c r="M19" s="45">
+      <c r="M19" s="22">
         <v>9</v>
       </c>
-      <c r="N19" s="45">
+      <c r="N19" s="22">
         <v>5</v>
       </c>
-      <c r="O19" s="45">
+      <c r="O19" s="22">
         <v>2</v>
       </c>
-      <c r="P19" s="45">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="45">
-        <v>1</v>
-      </c>
-      <c r="R19" s="47">
-        <v>1</v>
-      </c>
-      <c r="S19" s="45">
-        <v>1</v>
-      </c>
-      <c r="T19" s="45">
-        <v>1</v>
-      </c>
-      <c r="U19" s="45">
-        <v>1</v>
-      </c>
-      <c r="V19" s="45">
-        <v>0</v>
-      </c>
-      <c r="W19" s="45">
-        <v>0</v>
-      </c>
-      <c r="X19" s="45">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="45">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="45">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="45">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="45">
+      <c r="P19" s="22">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="22">
+        <v>1</v>
+      </c>
+      <c r="R19" s="22">
+        <v>1</v>
+      </c>
+      <c r="S19" s="22">
+        <v>1</v>
+      </c>
+      <c r="T19" s="22">
+        <v>1</v>
+      </c>
+      <c r="U19" s="22">
+        <v>1</v>
+      </c>
+      <c r="V19" s="22">
+        <v>0</v>
+      </c>
+      <c r="W19" s="22">
+        <v>0</v>
+      </c>
+      <c r="X19" s="22">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="22">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="22">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:28">
-      <c r="A20" s="33" t="s">
+      <c r="A20" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="45">
-        <v>0</v>
-      </c>
-      <c r="D20" s="45">
-        <v>0</v>
-      </c>
-      <c r="E20" s="45">
-        <v>0</v>
-      </c>
-      <c r="F20" s="45">
-        <v>0</v>
-      </c>
-      <c r="G20" s="48">
-        <v>0</v>
-      </c>
-      <c r="H20" s="48">
-        <v>0</v>
-      </c>
-      <c r="I20" s="41">
-        <v>0</v>
-      </c>
-      <c r="J20" s="48">
-        <v>0</v>
-      </c>
-      <c r="K20" s="48">
-        <v>0</v>
-      </c>
-      <c r="L20" s="48">
-        <v>0</v>
-      </c>
-      <c r="M20" s="48">
-        <v>0</v>
-      </c>
-      <c r="N20" s="48">
-        <v>0</v>
-      </c>
-      <c r="O20" s="48">
-        <v>0</v>
-      </c>
-      <c r="P20" s="48">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="48">
-        <v>0</v>
-      </c>
-      <c r="R20" s="49">
-        <v>0</v>
-      </c>
-      <c r="S20" s="48">
-        <v>0</v>
-      </c>
-      <c r="T20" s="48">
-        <v>0</v>
-      </c>
-      <c r="U20" s="48">
-        <v>0</v>
-      </c>
-      <c r="V20" s="48">
-        <v>0</v>
-      </c>
-      <c r="W20" s="48">
-        <v>0</v>
-      </c>
-      <c r="X20" s="48">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="48">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="48">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="48">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="48">
+      <c r="C20" s="22">
+        <v>0</v>
+      </c>
+      <c r="D20" s="22">
+        <v>0</v>
+      </c>
+      <c r="E20" s="22">
+        <v>0</v>
+      </c>
+      <c r="F20" s="22">
+        <v>0</v>
+      </c>
+      <c r="G20" s="23">
+        <v>0</v>
+      </c>
+      <c r="H20" s="23">
+        <v>0</v>
+      </c>
+      <c r="I20" s="14">
+        <v>0</v>
+      </c>
+      <c r="J20" s="23">
+        <v>0</v>
+      </c>
+      <c r="K20" s="23">
+        <v>0</v>
+      </c>
+      <c r="L20" s="23">
+        <v>0</v>
+      </c>
+      <c r="M20" s="23">
+        <v>0</v>
+      </c>
+      <c r="N20" s="23">
+        <v>0</v>
+      </c>
+      <c r="O20" s="23">
+        <v>0</v>
+      </c>
+      <c r="P20" s="23">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="23">
+        <v>0</v>
+      </c>
+      <c r="R20" s="23">
+        <v>0</v>
+      </c>
+      <c r="S20" s="23">
+        <v>0</v>
+      </c>
+      <c r="T20" s="23">
+        <v>0</v>
+      </c>
+      <c r="U20" s="23">
+        <v>0</v>
+      </c>
+      <c r="V20" s="23">
+        <v>0</v>
+      </c>
+      <c r="W20" s="23">
+        <v>0</v>
+      </c>
+      <c r="X20" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="23">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:28">
-      <c r="A21" s="33" t="s">
+      <c r="A21" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="45">
-        <v>0</v>
-      </c>
-      <c r="D21" s="45">
-        <v>0</v>
-      </c>
-      <c r="E21" s="45">
-        <v>0</v>
-      </c>
-      <c r="F21" s="45">
-        <v>0</v>
-      </c>
-      <c r="G21" s="48">
-        <v>0</v>
-      </c>
-      <c r="H21" s="45">
+      <c r="C21" s="22">
+        <v>0</v>
+      </c>
+      <c r="D21" s="22">
+        <v>0</v>
+      </c>
+      <c r="E21" s="22">
+        <v>0</v>
+      </c>
+      <c r="F21" s="22">
+        <v>0</v>
+      </c>
+      <c r="G21" s="23">
+        <v>0</v>
+      </c>
+      <c r="H21" s="22">
         <v>8</v>
       </c>
-      <c r="I21" s="46">
-        <v>0</v>
-      </c>
-      <c r="J21" s="45">
+      <c r="I21" s="14">
+        <v>0</v>
+      </c>
+      <c r="J21" s="22">
         <v>9</v>
       </c>
-      <c r="K21" s="45">
+      <c r="K21" s="22">
         <v>7</v>
       </c>
-      <c r="L21" s="45">
+      <c r="L21" s="22">
         <v>10</v>
       </c>
-      <c r="M21" s="45">
+      <c r="M21" s="22">
         <v>9</v>
       </c>
-      <c r="N21" s="45">
+      <c r="N21" s="22">
         <v>5</v>
       </c>
-      <c r="O21" s="45">
-        <v>1</v>
-      </c>
-      <c r="P21" s="45">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="45">
-        <v>1</v>
-      </c>
-      <c r="R21" s="47">
-        <v>1</v>
-      </c>
-      <c r="S21" s="45">
-        <v>1</v>
-      </c>
-      <c r="T21" s="45">
-        <v>0</v>
-      </c>
-      <c r="U21" s="45">
-        <v>0</v>
-      </c>
-      <c r="V21" s="45">
-        <v>0</v>
-      </c>
-      <c r="W21" s="45">
-        <v>0</v>
-      </c>
-      <c r="X21" s="45">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="45">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="45">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="45">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="45">
+      <c r="O21" s="22">
+        <v>1</v>
+      </c>
+      <c r="P21" s="22">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="22">
+        <v>1</v>
+      </c>
+      <c r="R21" s="22">
+        <v>1</v>
+      </c>
+      <c r="S21" s="22">
+        <v>1</v>
+      </c>
+      <c r="T21" s="22">
+        <v>0</v>
+      </c>
+      <c r="U21" s="22">
+        <v>0</v>
+      </c>
+      <c r="V21" s="22">
+        <v>0</v>
+      </c>
+      <c r="W21" s="22">
+        <v>0</v>
+      </c>
+      <c r="X21" s="22">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="22">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="22">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:28">
-      <c r="A22" s="33" t="s">
+      <c r="A22" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="33" t="s">
+      <c r="B22" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="45">
-        <v>0</v>
-      </c>
-      <c r="D22" s="45">
-        <v>0</v>
-      </c>
-      <c r="E22" s="45">
-        <v>0</v>
-      </c>
-      <c r="F22" s="45">
-        <v>0</v>
-      </c>
-      <c r="G22" s="45">
-        <v>0</v>
-      </c>
-      <c r="H22" s="45">
+      <c r="C22" s="22">
+        <v>0</v>
+      </c>
+      <c r="D22" s="22">
+        <v>0</v>
+      </c>
+      <c r="E22" s="22">
+        <v>0</v>
+      </c>
+      <c r="F22" s="22">
+        <v>0</v>
+      </c>
+      <c r="G22" s="22">
+        <v>0</v>
+      </c>
+      <c r="H22" s="22">
         <v>15</v>
       </c>
-      <c r="I22" s="46">
-        <v>0</v>
-      </c>
-      <c r="J22" s="45">
+      <c r="I22" s="14">
+        <v>0</v>
+      </c>
+      <c r="J22" s="22">
         <v>19</v>
       </c>
-      <c r="K22" s="45">
+      <c r="K22" s="22">
         <v>13</v>
       </c>
-      <c r="L22" s="45">
+      <c r="L22" s="22">
         <v>5</v>
       </c>
-      <c r="M22" s="45">
+      <c r="M22" s="22">
         <v>4</v>
       </c>
-      <c r="N22" s="45">
+      <c r="N22" s="22">
         <v>3</v>
       </c>
-      <c r="O22" s="45">
-        <v>1</v>
-      </c>
-      <c r="P22" s="45">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="45">
-        <v>0</v>
-      </c>
-      <c r="R22" s="47">
-        <v>0</v>
-      </c>
-      <c r="S22" s="45">
-        <v>0</v>
-      </c>
-      <c r="T22" s="45">
-        <v>0</v>
-      </c>
-      <c r="U22" s="45">
-        <v>0</v>
-      </c>
-      <c r="V22" s="45">
-        <v>0</v>
-      </c>
-      <c r="W22" s="45">
-        <v>0</v>
-      </c>
-      <c r="X22" s="45">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="45">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="45">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="45">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="45">
+      <c r="O22" s="22">
+        <v>1</v>
+      </c>
+      <c r="P22" s="22">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="22">
+        <v>0</v>
+      </c>
+      <c r="R22" s="22">
+        <v>0</v>
+      </c>
+      <c r="S22" s="22">
+        <v>0</v>
+      </c>
+      <c r="T22" s="22">
+        <v>0</v>
+      </c>
+      <c r="U22" s="22">
+        <v>0</v>
+      </c>
+      <c r="V22" s="22">
+        <v>0</v>
+      </c>
+      <c r="W22" s="22">
+        <v>0</v>
+      </c>
+      <c r="X22" s="22">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="22">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="22">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:28">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="39" t="s">
+      <c r="B23" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="50">
-        <v>0</v>
-      </c>
-      <c r="D23" s="50">
-        <v>0</v>
-      </c>
-      <c r="E23" s="50">
+      <c r="C23" s="24">
+        <v>0</v>
+      </c>
+      <c r="D23" s="24">
+        <v>0</v>
+      </c>
+      <c r="E23" s="24">
         <f>SUM(E14:E22)</f>
         <v>10</v>
       </c>
-      <c r="F23" s="50">
+      <c r="F23" s="24">
         <f t="shared" ref="F23:AB23" si="9">SUM(F14:F22)</f>
         <v>78</v>
       </c>
-      <c r="G23" s="50">
+      <c r="G23" s="24">
         <f t="shared" si="9"/>
         <v>115</v>
       </c>
-      <c r="H23" s="50">
+      <c r="H23" s="24">
         <f t="shared" si="9"/>
         <v>152</v>
       </c>
-      <c r="I23" s="50">
+      <c r="I23" s="24">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="J23" s="50">
+      <c r="J23" s="24">
         <f t="shared" si="9"/>
         <v>187</v>
       </c>
-      <c r="K23" s="50">
+      <c r="K23" s="24">
         <f t="shared" si="9"/>
         <v>132</v>
       </c>
-      <c r="L23" s="50">
+      <c r="L23" s="24">
         <f t="shared" si="9"/>
         <v>101</v>
       </c>
-      <c r="M23" s="50">
+      <c r="M23" s="24">
         <f t="shared" si="9"/>
         <v>86</v>
       </c>
-      <c r="N23" s="50">
+      <c r="N23" s="24">
         <f t="shared" si="9"/>
         <v>53</v>
       </c>
-      <c r="O23" s="50">
+      <c r="O23" s="24">
         <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="P23" s="50">
+      <c r="P23" s="24">
         <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="Q23" s="50">
+      <c r="Q23" s="24">
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="R23" s="50">
+      <c r="R23" s="24">
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="S23" s="50">
+      <c r="S23" s="24">
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="T23" s="50">
+      <c r="T23" s="24">
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="U23" s="50">
+      <c r="U23" s="24">
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="V23" s="50">
+      <c r="V23" s="24">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="W23" s="50">
+      <c r="W23" s="24">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="X23" s="50">
+      <c r="X23" s="24">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Y23" s="50">
+      <c r="Y23" s="24">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Z23" s="50">
+      <c r="Z23" s="24">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AA23" s="50">
+      <c r="AA23" s="24">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AB23" s="50">
+      <c r="AB23" s="24">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:28">
-      <c r="A24" s="42" t="s">
+      <c r="A24" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="51">
-        <v>0</v>
-      </c>
-      <c r="D24" s="51">
+      <c r="C24" s="25">
+        <v>0</v>
+      </c>
+      <c r="D24" s="25">
         <f>D23</f>
         <v>0</v>
       </c>
-      <c r="E24" s="51">
+      <c r="E24" s="25">
         <f>D24+E23</f>
         <v>10</v>
       </c>
-      <c r="F24" s="51">
+      <c r="F24" s="25">
         <f>E24+F23</f>
         <v>88</v>
       </c>
-      <c r="G24" s="51">
+      <c r="G24" s="25">
         <f>F24+G23</f>
         <v>203</v>
       </c>
-      <c r="H24" s="51">
+      <c r="H24" s="25">
         <f>G24+H23</f>
         <v>355</v>
       </c>
-      <c r="I24" s="46">
+      <c r="I24" s="25">
         <f t="shared" ref="I24:U24" si="10">H24+I23</f>
         <v>358</v>
       </c>
-      <c r="J24" s="51">
+      <c r="J24" s="25">
         <f t="shared" si="10"/>
         <v>545</v>
       </c>
-      <c r="K24" s="51">
+      <c r="K24" s="25">
         <f t="shared" si="10"/>
         <v>677</v>
       </c>
-      <c r="L24" s="51">
+      <c r="L24" s="25">
         <f t="shared" si="10"/>
         <v>778</v>
       </c>
-      <c r="M24" s="51">
+      <c r="M24" s="25">
         <f t="shared" si="10"/>
         <v>864</v>
       </c>
-      <c r="N24" s="51">
+      <c r="N24" s="25">
         <f t="shared" si="10"/>
         <v>917</v>
       </c>
-      <c r="O24" s="51">
+      <c r="O24" s="25">
         <f t="shared" si="10"/>
         <v>932</v>
       </c>
-      <c r="P24" s="51">
+      <c r="P24" s="25">
         <f t="shared" si="10"/>
         <v>939</v>
       </c>
-      <c r="Q24" s="51">
+      <c r="Q24" s="25">
         <f t="shared" si="10"/>
         <v>945</v>
       </c>
-      <c r="R24" s="51">
+      <c r="R24" s="25">
         <f t="shared" si="10"/>
         <v>951</v>
       </c>
-      <c r="S24" s="51">
+      <c r="S24" s="25">
         <f t="shared" si="10"/>
         <v>957</v>
       </c>
-      <c r="T24" s="51">
+      <c r="T24" s="25">
         <f t="shared" si="10"/>
         <v>962</v>
       </c>
-      <c r="U24" s="51">
+      <c r="U24" s="25">
         <f t="shared" si="10"/>
         <v>967</v>
       </c>
-      <c r="V24" s="51">
+      <c r="V24" s="25">
         <f t="shared" ref="V24" si="11">U24+V23</f>
         <v>970</v>
       </c>
-      <c r="W24" s="51">
+      <c r="W24" s="25">
         <f t="shared" ref="W24" si="12">V24+W23</f>
         <v>971</v>
       </c>
-      <c r="X24" s="51">
+      <c r="X24" s="25">
         <f t="shared" ref="X24" si="13">W24+X23</f>
         <v>971</v>
       </c>
-      <c r="Y24" s="51">
+      <c r="Y24" s="25">
         <f t="shared" ref="Y24" si="14">X24+Y23</f>
         <v>971</v>
       </c>
-      <c r="Z24" s="51">
+      <c r="Z24" s="25">
         <f t="shared" ref="Z24" si="15">Y24+Z23</f>
         <v>971</v>
       </c>
-      <c r="AA24" s="51">
+      <c r="AA24" s="25">
         <f t="shared" ref="AA24" si="16">Z24+AA23</f>
         <v>971</v>
       </c>
-      <c r="AB24" s="51">
+      <c r="AB24" s="25">
         <f t="shared" ref="AB24" si="17">AA24+AB23</f>
         <v>971</v>
       </c>
     </row>
     <row r="25" spans="1:28">
-      <c r="A25" s="42" t="s">
+      <c r="A25" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="51">
+      <c r="C25" s="25">
         <f>C13-C24</f>
         <v>0</v>
       </c>
-      <c r="D25" s="51">
+      <c r="D25" s="25">
         <f t="shared" ref="D25:W25" si="18">D13-D24</f>
         <v>2</v>
       </c>
-      <c r="E25" s="51">
+      <c r="E25" s="25">
         <f t="shared" si="18"/>
         <v>13</v>
       </c>
-      <c r="F25" s="51">
+      <c r="F25" s="25">
         <f t="shared" si="18"/>
         <v>93</v>
       </c>
-      <c r="G25" s="51">
+      <c r="G25" s="25">
         <f t="shared" si="18"/>
         <v>198</v>
       </c>
-      <c r="H25" s="51">
+      <c r="H25" s="25">
         <f t="shared" si="18"/>
         <v>252</v>
       </c>
-      <c r="I25" s="46">
+      <c r="I25" s="25">
         <f t="shared" si="18"/>
         <v>284</v>
       </c>
-      <c r="J25" s="51">
+      <c r="J25" s="25">
         <f t="shared" si="18"/>
         <v>218</v>
       </c>
-      <c r="K25" s="51">
+      <c r="K25" s="25">
         <f t="shared" si="18"/>
         <v>170</v>
       </c>
-      <c r="L25" s="51">
+      <c r="L25" s="25">
         <f t="shared" si="18"/>
         <v>124</v>
       </c>
-      <c r="M25" s="51">
+      <c r="M25" s="25">
         <f t="shared" si="18"/>
         <v>65</v>
       </c>
-      <c r="N25" s="51">
+      <c r="N25" s="25">
         <f t="shared" si="18"/>
         <v>29</v>
       </c>
-      <c r="O25" s="51">
+      <c r="O25" s="25">
         <f t="shared" si="18"/>
         <v>26</v>
       </c>
-      <c r="P25" s="51">
+      <c r="P25" s="25">
         <f t="shared" si="18"/>
         <v>26</v>
       </c>
-      <c r="Q25" s="51">
+      <c r="Q25" s="25">
         <f t="shared" si="18"/>
         <v>25</v>
       </c>
-      <c r="R25" s="51">
+      <c r="R25" s="25">
         <f t="shared" si="18"/>
         <v>23</v>
       </c>
-      <c r="S25" s="51">
+      <c r="S25" s="25">
         <f t="shared" si="18"/>
         <v>19</v>
       </c>
-      <c r="T25" s="51">
+      <c r="T25" s="25">
         <f t="shared" si="18"/>
         <v>15</v>
       </c>
-      <c r="U25" s="51">
+      <c r="U25" s="25">
         <f t="shared" si="18"/>
         <v>12</v>
       </c>
-      <c r="V25" s="51">
+      <c r="V25" s="25">
         <f t="shared" si="18"/>
         <v>10</v>
       </c>
-      <c r="W25" s="51">
+      <c r="W25" s="25">
         <f t="shared" si="18"/>
         <v>9</v>
       </c>
-      <c r="X25" s="51">
+      <c r="X25" s="25">
         <f t="shared" ref="X25:AB25" si="19">X13-X24</f>
         <v>9</v>
       </c>
-      <c r="Y25" s="51">
+      <c r="Y25" s="25">
         <f t="shared" si="19"/>
         <v>9</v>
       </c>
-      <c r="Z25" s="51">
+      <c r="Z25" s="25">
         <f t="shared" si="19"/>
         <v>9</v>
       </c>
-      <c r="AA25" s="51">
+      <c r="AA25" s="25">
         <f t="shared" si="19"/>
         <v>9</v>
       </c>
-      <c r="AB25" s="51">
+      <c r="AB25" s="25">
         <f t="shared" si="19"/>
         <v>9</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" spans="1:28">
-      <c r="A26" s="52" t="s">
+    <row r="26" spans="1:28">
+      <c r="A26" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="53"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53" t="s">
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13"/>
+      <c r="P26" s="13"/>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="13"/>
+      <c r="S26" s="13"/>
+      <c r="T26" s="13"/>
+      <c r="U26" s="13"/>
+      <c r="V26" s="13"/>
+      <c r="W26" s="13"/>
+      <c r="X26" s="13"/>
+      <c r="Y26" s="13"/>
+      <c r="Z26" s="13"/>
+      <c r="AA26" s="13"/>
+      <c r="AB26" s="13"/>
+    </row>
+    <row r="27" spans="1:28" ht="17">
+      <c r="A27" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="F26" s="54" t="s">
+      <c r="B27" s="45"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="45"/>
+      <c r="M27" s="45"/>
+      <c r="N27" s="45"/>
+      <c r="O27" s="45"/>
+      <c r="P27" s="45"/>
+      <c r="Q27" s="45"/>
+      <c r="R27" s="45"/>
+      <c r="S27" s="45"/>
+      <c r="T27" s="45"/>
+      <c r="U27" s="45"/>
+      <c r="V27" s="45"/>
+      <c r="W27" s="45"/>
+      <c r="X27" s="45"/>
+      <c r="Y27" s="45"/>
+      <c r="Z27" s="45"/>
+      <c r="AA27" s="45"/>
+      <c r="AB27" s="45"/>
+    </row>
+    <row r="28" spans="1:28" ht="17">
+      <c r="A28" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="G26" s="53" t="s">
+      <c r="B28" s="47"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="47"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="47"/>
+      <c r="K28" s="47"/>
+      <c r="L28" s="47"/>
+      <c r="M28" s="47"/>
+      <c r="N28" s="47"/>
+      <c r="O28" s="47"/>
+      <c r="P28" s="47"/>
+      <c r="Q28" s="47"/>
+      <c r="R28" s="47"/>
+      <c r="S28" s="47"/>
+      <c r="T28" s="47"/>
+      <c r="U28" s="47"/>
+      <c r="V28" s="47"/>
+      <c r="W28" s="47"/>
+      <c r="X28" s="47"/>
+      <c r="Y28" s="47"/>
+      <c r="Z28" s="47"/>
+      <c r="AA28" s="47"/>
+      <c r="AB28" s="47"/>
+    </row>
+    <row r="29" spans="1:28" ht="17">
+      <c r="A29" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="H26" s="53" t="s">
-        <v>61</v>
-      </c>
-      <c r="I26" s="53"/>
-      <c r="J26" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="K26" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="L26" s="53" t="s">
-        <v>64</v>
-      </c>
-      <c r="M26" s="53" t="s">
-        <v>65</v>
-      </c>
-      <c r="N26" s="53" t="s">
-        <v>66</v>
-      </c>
-      <c r="O26" s="53" t="s">
-        <v>67</v>
-      </c>
-      <c r="P26" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q26" s="53"/>
-      <c r="R26" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="S26" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="T26" s="53"/>
-      <c r="U26" s="53"/>
-      <c r="V26" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="W26" s="53"/>
-      <c r="X26" s="53" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y26" s="53"/>
-      <c r="Z26" s="53"/>
-      <c r="AA26" s="53"/>
-      <c r="AB26" s="53"/>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="1:28">
-      <c r="B27"/>
-      <c r="C27"/>
-      <c r="D27"/>
-      <c r="E27"/>
-      <c r="F27"/>
-      <c r="G27"/>
-      <c r="H27"/>
-      <c r="I27"/>
-      <c r="J27" s="53"/>
-      <c r="K27"/>
-      <c r="L27"/>
-      <c r="M27"/>
-      <c r="O27"/>
-      <c r="Q27" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="R27"/>
-      <c r="S27"/>
-      <c r="T27" s="55"/>
-      <c r="U27"/>
-      <c r="V27"/>
-      <c r="Y27" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="1:28">
-      <c r="A28" s="56" t="s">
-        <v>75</v>
-      </c>
-      <c r="B28" s="57"/>
-      <c r="C28" s="57"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="58">
-        <v>0.3</v>
-      </c>
-      <c r="H28" s="58"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="58"/>
-      <c r="K28" s="58">
-        <v>0.7</v>
-      </c>
-      <c r="L28" s="58"/>
-      <c r="M28" s="58">
-        <v>0.85</v>
-      </c>
-      <c r="N28" s="58"/>
-      <c r="O28" s="58">
-        <v>0.9</v>
-      </c>
-      <c r="P28" s="57"/>
-      <c r="Q28" s="57"/>
-      <c r="R28" s="57"/>
-      <c r="S28" s="58"/>
-      <c r="T28" s="58"/>
-      <c r="U28" s="58"/>
-      <c r="V28" s="57"/>
-      <c r="W28" s="58">
-        <v>0.99</v>
-      </c>
-      <c r="X28" s="58"/>
-      <c r="Y28" s="57"/>
-      <c r="Z28" s="58"/>
-      <c r="AA28" s="57"/>
-      <c r="AB28" s="57"/>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="1:28">
-      <c r="G29" s="1">
-        <f>$AD$13*G28</f>
-        <v>0</v>
-      </c>
-      <c r="K29" s="1">
-        <f t="shared" ref="K29:O29" si="20">$AD$13*K28</f>
-        <v>0</v>
-      </c>
-      <c r="M29" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O29" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="P29" s="59"/>
-      <c r="R29" s="59"/>
-      <c r="W29" s="1">
-        <f>$AD$13*W28</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="1:28">
-      <c r="A30" s="60" t="s">
-        <v>76</v>
-      </c>
-      <c r="B30" s="61"/>
-      <c r="C30" s="61"/>
-      <c r="D30" s="61"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="61"/>
-      <c r="G30" s="62">
-        <v>0.5</v>
-      </c>
-      <c r="H30" s="62"/>
-      <c r="I30" s="61"/>
-      <c r="J30" s="62"/>
-      <c r="K30" s="62">
-        <v>0.8</v>
-      </c>
-      <c r="L30" s="62"/>
-      <c r="M30" s="62">
-        <v>0.93</v>
-      </c>
-      <c r="N30" s="62"/>
-      <c r="O30" s="62" t="s">
-        <v>77</v>
-      </c>
-      <c r="P30" s="61"/>
-      <c r="Q30" s="61"/>
-      <c r="R30" s="61"/>
-      <c r="S30" s="62"/>
-      <c r="T30" s="62"/>
-      <c r="U30" s="62"/>
-      <c r="V30" s="61"/>
-      <c r="W30" s="61" t="s">
-        <v>78</v>
-      </c>
-      <c r="X30" s="61"/>
-      <c r="Y30" s="61"/>
-      <c r="Z30" s="61"/>
-      <c r="AA30" s="61"/>
-      <c r="AB30" s="61"/>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="1:28">
-      <c r="G31" s="1">
-        <f>G13*G30</f>
-        <v>200.5</v>
-      </c>
-      <c r="K31" s="1">
-        <f>K13*K30</f>
-        <v>677.6</v>
-      </c>
-      <c r="M31" s="1">
-        <f>M13*M30</f>
-        <v>863.97</v>
-      </c>
+      <c r="B29" s="49"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="49"/>
+      <c r="H29" s="49"/>
+      <c r="I29" s="49"/>
+      <c r="J29" s="49"/>
+      <c r="K29" s="49"/>
+      <c r="L29" s="49"/>
+      <c r="M29" s="49"/>
+      <c r="N29" s="49"/>
+      <c r="O29" s="49"/>
+      <c r="P29" s="49"/>
+      <c r="Q29" s="49"/>
+      <c r="R29" s="49"/>
+      <c r="S29" s="49"/>
+      <c r="T29" s="49"/>
+      <c r="U29" s="49"/>
+      <c r="V29" s="49"/>
+      <c r="W29" s="49"/>
+      <c r="X29" s="49"/>
+      <c r="Y29" s="49"/>
+      <c r="Z29" s="49"/>
+      <c r="AA29" s="49"/>
+      <c r="AB29" s="49"/>
     </row>
   </sheetData>
   <protectedRanges>
@@ -5035,35 +4360,32 @@
       <selection activeCell="L18" sqref="L18"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" orientation="portrait"/>
-      <headerFooter/>
     </customSheetView>
     <customSheetView guid="{D796FD1B-3799-48AB-9F20-11C8F0719461}" scale="115">
-      <pane xSplit="3" ySplit="4" topLeftCell="D5" activePane="bottomRight" state="frozen"/>
+      <pane xSplit="3" ySplit="4" topLeftCell="D5" state="frozen"/>
       <selection activeCell="R31" sqref="R31"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" orientation="portrait"/>
-      <headerFooter/>
     </customSheetView>
     <customSheetView guid="{A17EB640-8A85-4654-BB32-64D77149EF56}">
-      <pane xSplit="3" ySplit="4" topLeftCell="D5" activePane="bottomRight" state="frozen"/>
+      <pane xSplit="3" ySplit="4" topLeftCell="D5" state="frozen"/>
       <selection activeCell="AN18" sqref="AN18"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" orientation="portrait"/>
-      <headerFooter/>
     </customSheetView>
   </customSheetViews>
   <mergeCells count="6">
+    <mergeCell ref="Y1:AB1"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="K1:O1"/>
     <mergeCell ref="P1:S1"/>
     <mergeCell ref="T1:X1"/>
-    <mergeCell ref="Y1:AB1"/>
   </mergeCells>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
